--- a/sheets/국악이꽃피는나무/검수/쑥대머리.xlsx
+++ b/sheets/국악이꽃피는나무/검수/쑥대머리.xlsx
@@ -7469,7 +7469,7 @@
       </c>
       <c r="L26" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -7572,7 +7572,7 @@
       <c r="C28" s="24"/>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林○</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">

--- a/sheets/국악이꽃피는나무/검수/쑥대머리.xlsx
+++ b/sheets/국악이꽃피는나무/검수/쑥대머리.xlsx
@@ -6126,28 +6126,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="67.8" customHeight="true">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="100.96" customHeight="true">
+    <row r="3" ht="121.67" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="100.96" customHeight="true">
+    <row r="4" ht="121.67" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -6268,7 +6268,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="100.96" customHeight="true">
+    <row r="5" ht="121.67" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="100.96" customHeight="true">
+    <row r="6" ht="121.67" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="100.96" customHeight="true">
+    <row r="7" ht="121.67" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="100.96" customHeight="true">
+    <row r="8" ht="121.67" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="100.96" customHeight="true">
+    <row r="9" ht="121.67" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="100.96" customHeight="true">
+    <row r="10" ht="121.67" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="100.96" customHeight="true">
+    <row r="11" ht="121.67" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="100.96" customHeight="true">
+    <row r="12" ht="121.67" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="100.96" customHeight="true">
+    <row r="13" ht="121.67" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -6713,7 +6713,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="100.96" customHeight="true">
+    <row r="14" ht="121.67" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="67.8" customHeight="true">
+    <row r="16" ht="81.63" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="100.96" customHeight="true">
+    <row r="17" ht="121.67" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="100.96" customHeight="true">
+    <row r="18" ht="121.67" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="100.96" customHeight="true">
+    <row r="19" ht="121.67" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="100.96" customHeight="true">
+    <row r="20" ht="121.67" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="100.96" customHeight="true">
+    <row r="21" ht="121.67" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="100.96" customHeight="true">
+    <row r="22" ht="121.67" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="100.96" customHeight="true">
+    <row r="23" ht="121.67" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="100.96" customHeight="true">
+    <row r="24" ht="121.67" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="100.96" customHeight="true">
+    <row r="25" ht="121.67" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="100.96" customHeight="true">
+    <row r="26" ht="121.67" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="100.96" customHeight="true">
+    <row r="27" ht="121.67" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="100.96" customHeight="true">
+    <row r="28" ht="121.67" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
